--- a/docs/archive/Data_PIN_Karyawan_Digimasia_v2.xlsx
+++ b/docs/archive/Data_PIN_Karyawan_Digimasia_v2.xlsx
@@ -508,7 +508,7 @@
         <v>Candra Prasetyo</v>
       </c>
       <c r="B8" t="str">
-        <v>Content Design</v>
+        <v>Software Engineering &amp; QA</v>
       </c>
       <c r="C8" t="str">
         <v>1119</v>
